--- a/artfynd/A 60553-2025 artfynd.xlsx
+++ b/artfynd/A 60553-2025 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131129377</v>
+        <v>131129587</v>
       </c>
       <c r="B3" t="n">
-        <v>58167</v>
+        <v>56748</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,46 +801,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Segersjö, Nrk</t>
+          <t>Segersjö 1, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532355</v>
+        <v>532339</v>
       </c>
       <c r="R3" t="n">
-        <v>6559582</v>
+        <v>6559657</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,12 +868,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Skogsglänta</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,17 +898,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>David Alvunger, Enviro Planning</t>
+          <t>Alfred Olofsson, Enviro Planning</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131129587</v>
+        <v>131129377</v>
       </c>
       <c r="B4" t="n">
-        <v>56748</v>
+        <v>58167</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,50 +916,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Segersjö 1, Nrk</t>
+          <t>Segersjö, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532339</v>
+        <v>532355</v>
       </c>
       <c r="R4" t="n">
-        <v>6559657</v>
+        <v>6559582</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,17 +979,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Skogsglänta</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,14 +1004,14 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Enviro Planning</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131128956</v>
+        <v>131129356</v>
       </c>
       <c r="B5" t="n">
         <v>58256</v>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532356</v>
+        <v>532317</v>
       </c>
       <c r="R5" t="n">
-        <v>6559685</v>
+        <v>6559623</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,32 +1117,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131129319</v>
+        <v>131128956</v>
       </c>
       <c r="B6" t="n">
-        <v>58167</v>
+        <v>58256</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532341</v>
+        <v>532356</v>
       </c>
       <c r="R6" t="n">
-        <v>6559717</v>
+        <v>6559685</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,32 +1223,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131129356</v>
+        <v>131129319</v>
       </c>
       <c r="B7" t="n">
-        <v>58256</v>
+        <v>58167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532317</v>
+        <v>532341</v>
       </c>
       <c r="R7" t="n">
-        <v>6559623</v>
+        <v>6559717</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1435,7 +1435,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131128955</v>
+        <v>131128912</v>
       </c>
       <c r="B9" t="n">
         <v>58167</v>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532330</v>
+        <v>532359</v>
       </c>
       <c r="R9" t="n">
-        <v>6559652</v>
+        <v>6559727</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131128912</v>
+        <v>131128955</v>
       </c>
       <c r="B10" t="n">
         <v>58167</v>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532359</v>
+        <v>532330</v>
       </c>
       <c r="R10" t="n">
-        <v>6559727</v>
+        <v>6559652</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1965,7 +1965,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131128968</v>
+        <v>131129415</v>
       </c>
       <c r="B14" t="n">
         <v>58256</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532343</v>
+        <v>532437</v>
       </c>
       <c r="R14" t="n">
-        <v>6559583</v>
+        <v>6559564</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2039,12 +2039,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,7 +2071,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131129415</v>
+        <v>131128968</v>
       </c>
       <c r="B15" t="n">
         <v>58256</v>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532437</v>
+        <v>532343</v>
       </c>
       <c r="R15" t="n">
-        <v>6559564</v>
+        <v>6559583</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2145,12 +2145,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 60553-2025 artfynd.xlsx
+++ b/artfynd/A 60553-2025 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131129587</v>
+        <v>131129377</v>
       </c>
       <c r="B3" t="n">
-        <v>56748</v>
+        <v>58167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,50 +801,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Segersjö 1, Nrk</t>
+          <t>Segersjö, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532339</v>
+        <v>532355</v>
       </c>
       <c r="R3" t="n">
-        <v>6559657</v>
+        <v>6559582</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,17 +864,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Skogsglänta</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,17 +889,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Enviro Planning</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131129377</v>
+        <v>131129587</v>
       </c>
       <c r="B4" t="n">
-        <v>58167</v>
+        <v>56748</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,46 +907,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Segersjö, Nrk</t>
+          <t>Segersjö 1, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532355</v>
+        <v>532339</v>
       </c>
       <c r="R4" t="n">
-        <v>6559582</v>
+        <v>6559657</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,12 +974,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Skogsglänta</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,39 +1004,39 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>David Alvunger, Enviro Planning</t>
+          <t>Alfred Olofsson, Enviro Planning</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131129356</v>
+        <v>131129319</v>
       </c>
       <c r="B5" t="n">
-        <v>58256</v>
+        <v>58167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532317</v>
+        <v>532341</v>
       </c>
       <c r="R5" t="n">
-        <v>6559623</v>
+        <v>6559717</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1223,32 +1223,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131129319</v>
+        <v>131129356</v>
       </c>
       <c r="B7" t="n">
-        <v>58167</v>
+        <v>58256</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532341</v>
+        <v>532317</v>
       </c>
       <c r="R7" t="n">
-        <v>6559717</v>
+        <v>6559623</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1435,7 +1435,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131128912</v>
+        <v>131128955</v>
       </c>
       <c r="B9" t="n">
         <v>58167</v>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532359</v>
+        <v>532330</v>
       </c>
       <c r="R9" t="n">
-        <v>6559727</v>
+        <v>6559652</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131128955</v>
+        <v>131128912</v>
       </c>
       <c r="B10" t="n">
         <v>58167</v>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532330</v>
+        <v>532359</v>
       </c>
       <c r="R10" t="n">
-        <v>6559652</v>
+        <v>6559727</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1647,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131129360</v>
+        <v>131129373</v>
       </c>
       <c r="B11" t="n">
-        <v>58167</v>
+        <v>58367</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,21 +1658,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103012</v>
+        <v>103018</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532346</v>
+        <v>532335</v>
       </c>
       <c r="R11" t="n">
-        <v>6559649</v>
+        <v>6559541</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1753,7 +1753,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131129013</v>
+        <v>131129360</v>
       </c>
       <c r="B12" t="n">
         <v>58167</v>
@@ -1797,13 +1797,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532460</v>
+        <v>532346</v>
       </c>
       <c r="R12" t="n">
-        <v>6559584</v>
+        <v>6559649</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,10 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131129373</v>
+        <v>131129013</v>
       </c>
       <c r="B13" t="n">
-        <v>58367</v>
+        <v>58167</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103018</v>
+        <v>103012</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532335</v>
+        <v>532460</v>
       </c>
       <c r="R13" t="n">
-        <v>6559541</v>
+        <v>6559584</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1965,7 +1965,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131129415</v>
+        <v>131128968</v>
       </c>
       <c r="B14" t="n">
         <v>58256</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532437</v>
+        <v>532343</v>
       </c>
       <c r="R14" t="n">
-        <v>6559564</v>
+        <v>6559583</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2039,12 +2039,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,7 +2071,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131128968</v>
+        <v>131129415</v>
       </c>
       <c r="B15" t="n">
         <v>58256</v>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532343</v>
+        <v>532437</v>
       </c>
       <c r="R15" t="n">
-        <v>6559583</v>
+        <v>6559564</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2145,12 +2145,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 60553-2025 artfynd.xlsx
+++ b/artfynd/A 60553-2025 artfynd.xlsx
@@ -1011,32 +1011,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131129319</v>
+        <v>131128956</v>
       </c>
       <c r="B5" t="n">
-        <v>58167</v>
+        <v>58256</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532341</v>
+        <v>532356</v>
       </c>
       <c r="R5" t="n">
-        <v>6559717</v>
+        <v>6559685</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,32 +1117,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131128956</v>
+        <v>131129319</v>
       </c>
       <c r="B6" t="n">
-        <v>58256</v>
+        <v>58167</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532356</v>
+        <v>532341</v>
       </c>
       <c r="R6" t="n">
-        <v>6559685</v>
+        <v>6559717</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1647,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131129373</v>
+        <v>131129360</v>
       </c>
       <c r="B11" t="n">
-        <v>58367</v>
+        <v>58167</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,21 +1658,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103018</v>
+        <v>103012</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532335</v>
+        <v>532346</v>
       </c>
       <c r="R11" t="n">
-        <v>6559541</v>
+        <v>6559649</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1753,7 +1753,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131129360</v>
+        <v>131129013</v>
       </c>
       <c r="B12" t="n">
         <v>58167</v>
@@ -1797,13 +1797,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532346</v>
+        <v>532460</v>
       </c>
       <c r="R12" t="n">
-        <v>6559649</v>
+        <v>6559584</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,10 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131129013</v>
+        <v>131129373</v>
       </c>
       <c r="B13" t="n">
-        <v>58167</v>
+        <v>58367</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103012</v>
+        <v>103018</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532460</v>
+        <v>532335</v>
       </c>
       <c r="R13" t="n">
-        <v>6559584</v>
+        <v>6559541</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 60553-2025 artfynd.xlsx
+++ b/artfynd/A 60553-2025 artfynd.xlsx
@@ -1011,32 +1011,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131128956</v>
+        <v>131129319</v>
       </c>
       <c r="B5" t="n">
-        <v>58256</v>
+        <v>58167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532356</v>
+        <v>532341</v>
       </c>
       <c r="R5" t="n">
-        <v>6559685</v>
+        <v>6559717</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,32 +1117,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131129319</v>
+        <v>131129356</v>
       </c>
       <c r="B6" t="n">
-        <v>58167</v>
+        <v>58256</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532341</v>
+        <v>532317</v>
       </c>
       <c r="R6" t="n">
-        <v>6559717</v>
+        <v>6559623</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1223,7 +1223,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131129356</v>
+        <v>131128956</v>
       </c>
       <c r="B7" t="n">
         <v>58256</v>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532317</v>
+        <v>532356</v>
       </c>
       <c r="R7" t="n">
-        <v>6559623</v>
+        <v>6559685</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1965,7 +1965,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131128968</v>
+        <v>131129415</v>
       </c>
       <c r="B14" t="n">
         <v>58256</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532343</v>
+        <v>532437</v>
       </c>
       <c r="R14" t="n">
-        <v>6559583</v>
+        <v>6559564</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2039,12 +2039,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,7 +2071,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131129415</v>
+        <v>131128968</v>
       </c>
       <c r="B15" t="n">
         <v>58256</v>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532437</v>
+        <v>532343</v>
       </c>
       <c r="R15" t="n">
-        <v>6559564</v>
+        <v>6559583</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2145,12 +2145,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2398,10 +2398,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131129375</v>
+        <v>131129574</v>
       </c>
       <c r="B18" t="n">
-        <v>58256</v>
+        <v>56755</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2409,21 +2409,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>205992</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2431,24 +2431,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Segersjö, Nrk</t>
+          <t>Segersjö 1, Nrk</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532358</v>
+        <v>532339</v>
       </c>
       <c r="R18" t="n">
-        <v>6559555</v>
+        <v>6559657</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2472,12 +2476,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Skogsglänta</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,17 +2506,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>David Alvunger, Enviro Planning</t>
+          <t>Alfred Olofsson, Enviro Planning</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131129574</v>
+        <v>131129375</v>
       </c>
       <c r="B19" t="n">
-        <v>56755</v>
+        <v>58256</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,21 +2524,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205992</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2537,28 +2546,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Segersjö 1, Nrk</t>
+          <t>Segersjö, Nrk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532339</v>
+        <v>532358</v>
       </c>
       <c r="R19" t="n">
-        <v>6559657</v>
+        <v>6559555</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2582,17 +2587,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Skogsglänta</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Enviro Planning</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 60553-2025 artfynd.xlsx
+++ b/artfynd/A 60553-2025 artfynd.xlsx
@@ -1011,32 +1011,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131129319</v>
+        <v>131128956</v>
       </c>
       <c r="B5" t="n">
-        <v>58167</v>
+        <v>58256</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532341</v>
+        <v>532356</v>
       </c>
       <c r="R5" t="n">
-        <v>6559717</v>
+        <v>6559685</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1223,32 +1223,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131128956</v>
+        <v>131129319</v>
       </c>
       <c r="B7" t="n">
-        <v>58256</v>
+        <v>58167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532356</v>
+        <v>532341</v>
       </c>
       <c r="R7" t="n">
-        <v>6559685</v>
+        <v>6559717</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1435,7 +1435,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131128955</v>
+        <v>131128912</v>
       </c>
       <c r="B9" t="n">
         <v>58167</v>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532330</v>
+        <v>532359</v>
       </c>
       <c r="R9" t="n">
-        <v>6559652</v>
+        <v>6559727</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131128912</v>
+        <v>131128955</v>
       </c>
       <c r="B10" t="n">
         <v>58167</v>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532359</v>
+        <v>532330</v>
       </c>
       <c r="R10" t="n">
-        <v>6559727</v>
+        <v>6559652</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1647,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131129360</v>
+        <v>131129373</v>
       </c>
       <c r="B11" t="n">
-        <v>58167</v>
+        <v>58367</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,21 +1658,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103012</v>
+        <v>103018</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532346</v>
+        <v>532335</v>
       </c>
       <c r="R11" t="n">
-        <v>6559649</v>
+        <v>6559541</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1753,7 +1753,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131129013</v>
+        <v>131129360</v>
       </c>
       <c r="B12" t="n">
         <v>58167</v>
@@ -1797,13 +1797,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532460</v>
+        <v>532346</v>
       </c>
       <c r="R12" t="n">
-        <v>6559584</v>
+        <v>6559649</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,10 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131129373</v>
+        <v>131129013</v>
       </c>
       <c r="B13" t="n">
-        <v>58367</v>
+        <v>58167</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103018</v>
+        <v>103012</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532335</v>
+        <v>532460</v>
       </c>
       <c r="R13" t="n">
-        <v>6559541</v>
+        <v>6559584</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1965,7 +1965,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131129415</v>
+        <v>131128968</v>
       </c>
       <c r="B14" t="n">
         <v>58256</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532437</v>
+        <v>532343</v>
       </c>
       <c r="R14" t="n">
-        <v>6559564</v>
+        <v>6559583</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2039,12 +2039,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,7 +2071,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131128968</v>
+        <v>131129415</v>
       </c>
       <c r="B15" t="n">
         <v>58256</v>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532343</v>
+        <v>532437</v>
       </c>
       <c r="R15" t="n">
-        <v>6559583</v>
+        <v>6559564</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2145,12 +2145,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2398,10 +2398,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131129574</v>
+        <v>131129375</v>
       </c>
       <c r="B18" t="n">
-        <v>56755</v>
+        <v>58256</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2409,21 +2409,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>205992</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2431,28 +2431,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Segersjö 1, Nrk</t>
+          <t>Segersjö, Nrk</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532339</v>
+        <v>532358</v>
       </c>
       <c r="R18" t="n">
-        <v>6559657</v>
+        <v>6559555</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2476,17 +2472,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Skogsglänta</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2506,17 +2497,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Enviro Planning</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131129375</v>
+        <v>131129574</v>
       </c>
       <c r="B19" t="n">
-        <v>58256</v>
+        <v>56755</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,21 +2515,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>205992</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2546,24 +2537,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Segersjö, Nrk</t>
+          <t>Segersjö 1, Nrk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532358</v>
+        <v>532339</v>
       </c>
       <c r="R19" t="n">
-        <v>6559555</v>
+        <v>6559657</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2587,12 +2582,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Skogsglänta</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>David Alvunger, Enviro Planning</t>
+          <t>Alfred Olofsson, Enviro Planning</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 60553-2025 artfynd.xlsx
+++ b/artfynd/A 60553-2025 artfynd.xlsx
@@ -1117,32 +1117,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131129356</v>
+        <v>131129319</v>
       </c>
       <c r="B6" t="n">
-        <v>58256</v>
+        <v>58167</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532317</v>
+        <v>532341</v>
       </c>
       <c r="R6" t="n">
-        <v>6559623</v>
+        <v>6559717</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1223,32 +1223,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131129319</v>
+        <v>131129356</v>
       </c>
       <c r="B7" t="n">
-        <v>58167</v>
+        <v>58256</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532341</v>
+        <v>532317</v>
       </c>
       <c r="R7" t="n">
-        <v>6559717</v>
+        <v>6559623</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1435,7 +1435,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131128912</v>
+        <v>131128955</v>
       </c>
       <c r="B9" t="n">
         <v>58167</v>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532359</v>
+        <v>532330</v>
       </c>
       <c r="R9" t="n">
-        <v>6559727</v>
+        <v>6559652</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131128955</v>
+        <v>131128912</v>
       </c>
       <c r="B10" t="n">
         <v>58167</v>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532330</v>
+        <v>532359</v>
       </c>
       <c r="R10" t="n">
-        <v>6559652</v>
+        <v>6559727</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1647,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131129373</v>
+        <v>131129360</v>
       </c>
       <c r="B11" t="n">
-        <v>58367</v>
+        <v>58167</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,21 +1658,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103018</v>
+        <v>103012</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532335</v>
+        <v>532346</v>
       </c>
       <c r="R11" t="n">
-        <v>6559541</v>
+        <v>6559649</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1753,7 +1753,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131129360</v>
+        <v>131129013</v>
       </c>
       <c r="B12" t="n">
         <v>58167</v>
@@ -1797,13 +1797,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532346</v>
+        <v>532460</v>
       </c>
       <c r="R12" t="n">
-        <v>6559649</v>
+        <v>6559584</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,10 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131129013</v>
+        <v>131129373</v>
       </c>
       <c r="B13" t="n">
-        <v>58167</v>
+        <v>58367</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103012</v>
+        <v>103018</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532460</v>
+        <v>532335</v>
       </c>
       <c r="R13" t="n">
-        <v>6559584</v>
+        <v>6559541</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 60553-2025 artfynd.xlsx
+++ b/artfynd/A 60553-2025 artfynd.xlsx
@@ -1110,7 +1110,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>David Alvunger, Enviro Planning</t>
+          <t>Enviro Planning, David Alvunger</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>David Alvunger, Enviro Planning</t>
+          <t>Enviro Planning, David Alvunger</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>David Alvunger, Enviro Planning</t>
+          <t>Enviro Planning, David Alvunger</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>David Alvunger, Enviro Planning</t>
+          <t>Enviro Planning, David Alvunger</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2398,10 +2398,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131129375</v>
+        <v>131129574</v>
       </c>
       <c r="B18" t="n">
-        <v>58256</v>
+        <v>56755</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2409,21 +2409,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>205992</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2431,24 +2431,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Segersjö, Nrk</t>
+          <t>Segersjö 1, Nrk</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532358</v>
+        <v>532339</v>
       </c>
       <c r="R18" t="n">
-        <v>6559555</v>
+        <v>6559657</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2472,12 +2476,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Skogsglänta</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,17 +2506,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>David Alvunger, Enviro Planning</t>
+          <t>Alfred Olofsson, Enviro Planning</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131129574</v>
+        <v>131129375</v>
       </c>
       <c r="B19" t="n">
-        <v>56755</v>
+        <v>58256</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,21 +2524,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205992</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2537,28 +2546,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Segersjö 1, Nrk</t>
+          <t>Segersjö, Nrk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532339</v>
+        <v>532358</v>
       </c>
       <c r="R19" t="n">
-        <v>6559657</v>
+        <v>6559555</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2582,17 +2587,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Skogsglänta</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Enviro Planning</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>David Alvunger, Enviro Planning</t>
+          <t>Enviro Planning, David Alvunger</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 60553-2025 artfynd.xlsx
+++ b/artfynd/A 60553-2025 artfynd.xlsx
@@ -783,17 +783,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Enviro Planning</t>
+          <t>Enviro Planning, Alfred Olofsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131129377</v>
+        <v>131129587</v>
       </c>
       <c r="B3" t="n">
-        <v>58167</v>
+        <v>56748</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,46 +801,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Segersjö, Nrk</t>
+          <t>Segersjö 1, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532355</v>
+        <v>532339</v>
       </c>
       <c r="R3" t="n">
-        <v>6559582</v>
+        <v>6559657</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,12 +868,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Skogsglänta</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,17 +898,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>David Alvunger, Enviro Planning</t>
+          <t>Enviro Planning, Alfred Olofsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131129587</v>
+        <v>131129377</v>
       </c>
       <c r="B4" t="n">
-        <v>56748</v>
+        <v>58167</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,50 +916,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Segersjö 1, Nrk</t>
+          <t>Segersjö, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532339</v>
+        <v>532355</v>
       </c>
       <c r="R4" t="n">
-        <v>6559657</v>
+        <v>6559582</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,17 +979,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Skogsglänta</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,39 +1004,39 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Enviro Planning</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131128956</v>
+        <v>131129319</v>
       </c>
       <c r="B5" t="n">
-        <v>58256</v>
+        <v>58167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532356</v>
+        <v>532341</v>
       </c>
       <c r="R5" t="n">
-        <v>6559685</v>
+        <v>6559717</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,39 +1110,39 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Enviro Planning, David Alvunger</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131129319</v>
+        <v>131128956</v>
       </c>
       <c r="B6" t="n">
-        <v>58167</v>
+        <v>58256</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532341</v>
+        <v>532356</v>
       </c>
       <c r="R6" t="n">
-        <v>6559717</v>
+        <v>6559685</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Enviro Planning, David Alvunger</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1640,17 +1640,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>David Alvunger, Enviro Planning</t>
+          <t>Enviro Planning, David Alvunger</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131129360</v>
+        <v>131129373</v>
       </c>
       <c r="B11" t="n">
-        <v>58167</v>
+        <v>58368</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,21 +1658,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103012</v>
+        <v>103018</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532346</v>
+        <v>532335</v>
       </c>
       <c r="R11" t="n">
-        <v>6559649</v>
+        <v>6559541</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1753,7 +1753,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131129013</v>
+        <v>131129360</v>
       </c>
       <c r="B12" t="n">
         <v>58167</v>
@@ -1797,13 +1797,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532460</v>
+        <v>532346</v>
       </c>
       <c r="R12" t="n">
-        <v>6559584</v>
+        <v>6559649</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,10 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131129373</v>
+        <v>131129013</v>
       </c>
       <c r="B13" t="n">
-        <v>58367</v>
+        <v>58167</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103018</v>
+        <v>103012</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532335</v>
+        <v>532460</v>
       </c>
       <c r="R13" t="n">
-        <v>6559541</v>
+        <v>6559584</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Enviro Planning, David Alvunger</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Enviro Planning, David Alvunger</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2391,17 +2391,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Enviro Planning</t>
+          <t>Enviro Planning, Alfred Olofsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131129574</v>
+        <v>131129375</v>
       </c>
       <c r="B18" t="n">
-        <v>56755</v>
+        <v>58256</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2409,21 +2409,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>205992</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2431,28 +2431,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Segersjö 1, Nrk</t>
+          <t>Segersjö, Nrk</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532339</v>
+        <v>532358</v>
       </c>
       <c r="R18" t="n">
-        <v>6559657</v>
+        <v>6559555</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2476,17 +2472,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Skogsglänta</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2506,17 +2497,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Enviro Planning</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131129375</v>
+        <v>131129574</v>
       </c>
       <c r="B19" t="n">
-        <v>58256</v>
+        <v>56755</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,21 +2515,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>205992</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2546,24 +2537,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Segersjö, Nrk</t>
+          <t>Segersjö 1, Nrk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532358</v>
+        <v>532339</v>
       </c>
       <c r="R19" t="n">
-        <v>6559555</v>
+        <v>6559657</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2587,12 +2582,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Skogsglänta</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>David Alvunger, Enviro Planning</t>
+          <t>Alfred Olofsson, Enviro Planning</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2622,7 +2622,7 @@
         <v>131129383</v>
       </c>
       <c r="B20" t="n">
-        <v>58564</v>
+        <v>58565</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Enviro Planning, David Alvunger</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 60553-2025 artfynd.xlsx
+++ b/artfynd/A 60553-2025 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131129587</v>
+        <v>131129377</v>
       </c>
       <c r="B3" t="n">
-        <v>56748</v>
+        <v>58167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,50 +801,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Segersjö 1, Nrk</t>
+          <t>Segersjö, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532339</v>
+        <v>532355</v>
       </c>
       <c r="R3" t="n">
-        <v>6559657</v>
+        <v>6559582</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,17 +864,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Skogsglänta</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,17 +889,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Enviro Planning, Alfred Olofsson</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131129377</v>
+        <v>131129587</v>
       </c>
       <c r="B4" t="n">
-        <v>58167</v>
+        <v>56748</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,46 +907,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Segersjö, Nrk</t>
+          <t>Segersjö 1, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532355</v>
+        <v>532339</v>
       </c>
       <c r="R4" t="n">
-        <v>6559582</v>
+        <v>6559657</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,12 +974,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Skogsglänta</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>David Alvunger, Enviro Planning</t>
+          <t>Enviro Planning, Alfred Olofsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 60553-2025 artfynd.xlsx
+++ b/artfynd/A 60553-2025 artfynd.xlsx
@@ -783,7 +783,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Enviro Planning, Alfred Olofsson</t>
+          <t>Alfred Olofsson, Enviro Planning</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -1004,39 +1004,39 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Enviro Planning, Alfred Olofsson</t>
+          <t>Alfred Olofsson, Enviro Planning</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131129319</v>
+        <v>131128956</v>
       </c>
       <c r="B5" t="n">
-        <v>58167</v>
+        <v>58256</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532341</v>
+        <v>532356</v>
       </c>
       <c r="R5" t="n">
-        <v>6559717</v>
+        <v>6559685</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,7 +1117,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131128956</v>
+        <v>131129356</v>
       </c>
       <c r="B6" t="n">
         <v>58256</v>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532356</v>
+        <v>532317</v>
       </c>
       <c r="R6" t="n">
-        <v>6559685</v>
+        <v>6559623</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,32 +1223,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131129356</v>
+        <v>131129319</v>
       </c>
       <c r="B7" t="n">
-        <v>58256</v>
+        <v>58167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532317</v>
+        <v>532341</v>
       </c>
       <c r="R7" t="n">
-        <v>6559623</v>
+        <v>6559717</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1435,7 +1435,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131128955</v>
+        <v>131128912</v>
       </c>
       <c r="B9" t="n">
         <v>58167</v>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532330</v>
+        <v>532359</v>
       </c>
       <c r="R9" t="n">
-        <v>6559652</v>
+        <v>6559727</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131128912</v>
+        <v>131128955</v>
       </c>
       <c r="B10" t="n">
         <v>58167</v>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532359</v>
+        <v>532330</v>
       </c>
       <c r="R10" t="n">
-        <v>6559727</v>
+        <v>6559652</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Enviro Planning, David Alvunger</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1965,7 +1965,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131128968</v>
+        <v>131129415</v>
       </c>
       <c r="B14" t="n">
         <v>58256</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532343</v>
+        <v>532437</v>
       </c>
       <c r="R14" t="n">
-        <v>6559583</v>
+        <v>6559564</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2039,12 +2039,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,7 +2071,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131129415</v>
+        <v>131128968</v>
       </c>
       <c r="B15" t="n">
         <v>58256</v>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532437</v>
+        <v>532343</v>
       </c>
       <c r="R15" t="n">
-        <v>6559564</v>
+        <v>6559583</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2145,12 +2145,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Enviro Planning, Alfred Olofsson</t>
+          <t>Alfred Olofsson, Enviro Planning</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 60553-2025 artfynd.xlsx
+++ b/artfynd/A 60553-2025 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131129377</v>
+        <v>131129587</v>
       </c>
       <c r="B3" t="n">
-        <v>58167</v>
+        <v>56748</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,46 +801,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Segersjö, Nrk</t>
+          <t>Segersjö 1, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532355</v>
+        <v>532339</v>
       </c>
       <c r="R3" t="n">
-        <v>6559582</v>
+        <v>6559657</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,12 +868,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Skogsglänta</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,17 +898,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>David Alvunger, Enviro Planning</t>
+          <t>Alfred Olofsson, Enviro Planning</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131129587</v>
+        <v>131129377</v>
       </c>
       <c r="B4" t="n">
-        <v>56748</v>
+        <v>58167</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,50 +916,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Segersjö 1, Nrk</t>
+          <t>Segersjö, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532339</v>
+        <v>532355</v>
       </c>
       <c r="R4" t="n">
-        <v>6559657</v>
+        <v>6559582</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,17 +979,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Skogsglänta</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,39 +1004,39 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Enviro Planning</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131128956</v>
+        <v>131129319</v>
       </c>
       <c r="B5" t="n">
-        <v>58256</v>
+        <v>58167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532356</v>
+        <v>532341</v>
       </c>
       <c r="R5" t="n">
-        <v>6559685</v>
+        <v>6559717</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,7 +1117,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131129356</v>
+        <v>131128956</v>
       </c>
       <c r="B6" t="n">
         <v>58256</v>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532317</v>
+        <v>532356</v>
       </c>
       <c r="R6" t="n">
-        <v>6559623</v>
+        <v>6559685</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,32 +1223,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131129319</v>
+        <v>131129356</v>
       </c>
       <c r="B7" t="n">
-        <v>58167</v>
+        <v>58256</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532341</v>
+        <v>532317</v>
       </c>
       <c r="R7" t="n">
-        <v>6559717</v>
+        <v>6559623</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1647,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131129373</v>
+        <v>131129360</v>
       </c>
       <c r="B11" t="n">
-        <v>58368</v>
+        <v>58167</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,21 +1658,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103018</v>
+        <v>103012</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532335</v>
+        <v>532346</v>
       </c>
       <c r="R11" t="n">
-        <v>6559541</v>
+        <v>6559649</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1753,7 +1753,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131129360</v>
+        <v>131129013</v>
       </c>
       <c r="B12" t="n">
         <v>58167</v>
@@ -1797,13 +1797,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532346</v>
+        <v>532460</v>
       </c>
       <c r="R12" t="n">
-        <v>6559649</v>
+        <v>6559584</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,10 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131129013</v>
+        <v>131129373</v>
       </c>
       <c r="B13" t="n">
-        <v>58167</v>
+        <v>58368</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103012</v>
+        <v>103018</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532460</v>
+        <v>532335</v>
       </c>
       <c r="R13" t="n">
-        <v>6559584</v>
+        <v>6559541</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1965,7 +1965,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131129415</v>
+        <v>131128968</v>
       </c>
       <c r="B14" t="n">
         <v>58256</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532437</v>
+        <v>532343</v>
       </c>
       <c r="R14" t="n">
-        <v>6559564</v>
+        <v>6559583</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2039,12 +2039,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,7 +2071,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131128968</v>
+        <v>131129415</v>
       </c>
       <c r="B15" t="n">
         <v>58256</v>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532343</v>
+        <v>532437</v>
       </c>
       <c r="R15" t="n">
-        <v>6559583</v>
+        <v>6559564</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2145,12 +2145,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 60553-2025 artfynd.xlsx
+++ b/artfynd/A 60553-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131129561</v>
       </c>
       <c r="B2" t="n">
-        <v>56762</v>
+        <v>56764</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>131129587</v>
       </c>
       <c r="B3" t="n">
-        <v>56748</v>
+        <v>56750</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>131129377</v>
       </c>
       <c r="B4" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,32 +1011,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131129319</v>
+        <v>131129356</v>
       </c>
       <c r="B5" t="n">
-        <v>58167</v>
+        <v>58258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532341</v>
+        <v>532317</v>
       </c>
       <c r="R5" t="n">
-        <v>6559717</v>
+        <v>6559623</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1117,32 +1117,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131128956</v>
+        <v>131129319</v>
       </c>
       <c r="B6" t="n">
-        <v>58256</v>
+        <v>58169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532356</v>
+        <v>532341</v>
       </c>
       <c r="R6" t="n">
-        <v>6559685</v>
+        <v>6559717</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,10 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131129356</v>
+        <v>131128956</v>
       </c>
       <c r="B7" t="n">
-        <v>58256</v>
+        <v>58258</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532317</v>
+        <v>532356</v>
       </c>
       <c r="R7" t="n">
-        <v>6559623</v>
+        <v>6559685</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Alvunger, Enviro Planning</t>
+          <t>Enviro Planning, David Alvunger</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1332,7 +1332,7 @@
         <v>131129381</v>
       </c>
       <c r="B8" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131128912</v>
+        <v>131128955</v>
       </c>
       <c r="B9" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532359</v>
+        <v>532330</v>
       </c>
       <c r="R9" t="n">
-        <v>6559727</v>
+        <v>6559652</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,17 +1534,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>David Alvunger, Enviro Planning</t>
+          <t>Enviro Planning, David Alvunger</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131128955</v>
+        <v>131128912</v>
       </c>
       <c r="B10" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532330</v>
+        <v>532359</v>
       </c>
       <c r="R10" t="n">
-        <v>6559652</v>
+        <v>6559727</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1650,7 +1650,7 @@
         <v>131129360</v>
       </c>
       <c r="B11" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>131129013</v>
       </c>
       <c r="B12" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>David Alvunger, Enviro Planning</t>
+          <t>Enviro Planning, David Alvunger</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1862,7 +1862,7 @@
         <v>131129373</v>
       </c>
       <c r="B13" t="n">
-        <v>58368</v>
+        <v>58370</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>131128968</v>
       </c>
       <c r="B14" t="n">
-        <v>58256</v>
+        <v>58258</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>David Alvunger, Enviro Planning</t>
+          <t>Enviro Planning, David Alvunger</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2074,7 +2074,7 @@
         <v>131129415</v>
       </c>
       <c r="B15" t="n">
-        <v>58256</v>
+        <v>58258</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>131128965</v>
       </c>
       <c r="B16" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>David Alvunger, Enviro Planning</t>
+          <t>Enviro Planning, David Alvunger</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2286,7 +2286,7 @@
         <v>131129545</v>
       </c>
       <c r="B17" t="n">
-        <v>56767</v>
+        <v>56769</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>131129375</v>
       </c>
       <c r="B18" t="n">
-        <v>58256</v>
+        <v>58258</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>131129574</v>
       </c>
       <c r="B19" t="n">
-        <v>56755</v>
+        <v>56757</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>131129383</v>
       </c>
       <c r="B20" t="n">
-        <v>58565</v>
+        <v>58567</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>131128969</v>
       </c>
       <c r="B21" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>David Alvunger, Enviro Planning</t>
+          <t>Enviro Planning, David Alvunger</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 60553-2025 artfynd.xlsx
+++ b/artfynd/A 60553-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131129561</v>
       </c>
       <c r="B2" t="n">
-        <v>56764</v>
+        <v>56765</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131129587</v>
+        <v>131129377</v>
       </c>
       <c r="B3" t="n">
-        <v>56750</v>
+        <v>58170</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,50 +801,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Segersjö 1, Nrk</t>
+          <t>Segersjö, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532339</v>
+        <v>532355</v>
       </c>
       <c r="R3" t="n">
-        <v>6559657</v>
+        <v>6559582</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,17 +864,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Skogsglänta</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,17 +889,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Enviro Planning</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131129377</v>
+        <v>131129587</v>
       </c>
       <c r="B4" t="n">
-        <v>58169</v>
+        <v>56751</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,46 +907,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Segersjö, Nrk</t>
+          <t>Segersjö 1, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532355</v>
+        <v>532339</v>
       </c>
       <c r="R4" t="n">
-        <v>6559582</v>
+        <v>6559657</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,12 +974,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Skogsglänta</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,17 +1004,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>David Alvunger, Enviro Planning</t>
+          <t>Alfred Olofsson, Enviro Planning</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131129356</v>
+        <v>131128956</v>
       </c>
       <c r="B5" t="n">
-        <v>58258</v>
+        <v>58259</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532317</v>
+        <v>532356</v>
       </c>
       <c r="R5" t="n">
-        <v>6559623</v>
+        <v>6559685</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,32 +1117,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131129319</v>
+        <v>131129356</v>
       </c>
       <c r="B6" t="n">
-        <v>58169</v>
+        <v>58259</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532341</v>
+        <v>532317</v>
       </c>
       <c r="R6" t="n">
-        <v>6559717</v>
+        <v>6559623</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1223,32 +1223,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131128956</v>
+        <v>131129319</v>
       </c>
       <c r="B7" t="n">
-        <v>58258</v>
+        <v>58170</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532356</v>
+        <v>532341</v>
       </c>
       <c r="R7" t="n">
-        <v>6559685</v>
+        <v>6559717</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Enviro Planning, David Alvunger</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1332,7 +1332,7 @@
         <v>131129381</v>
       </c>
       <c r="B8" t="n">
-        <v>58169</v>
+        <v>58170</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>131128955</v>
       </c>
       <c r="B9" t="n">
-        <v>58169</v>
+        <v>58170</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Enviro Planning, David Alvunger</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1544,7 +1544,7 @@
         <v>131128912</v>
       </c>
       <c r="B10" t="n">
-        <v>58169</v>
+        <v>58170</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131129360</v>
+        <v>131129373</v>
       </c>
       <c r="B11" t="n">
-        <v>58169</v>
+        <v>58371</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,21 +1658,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103012</v>
+        <v>103018</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532346</v>
+        <v>532335</v>
       </c>
       <c r="R11" t="n">
-        <v>6559649</v>
+        <v>6559541</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131129013</v>
+        <v>131129360</v>
       </c>
       <c r="B12" t="n">
-        <v>58169</v>
+        <v>58170</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1797,13 +1797,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532460</v>
+        <v>532346</v>
       </c>
       <c r="R12" t="n">
-        <v>6559584</v>
+        <v>6559649</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,17 +1852,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Enviro Planning, David Alvunger</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131129373</v>
+        <v>131129013</v>
       </c>
       <c r="B13" t="n">
-        <v>58370</v>
+        <v>58170</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103018</v>
+        <v>103012</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532335</v>
+        <v>532460</v>
       </c>
       <c r="R13" t="n">
-        <v>6559541</v>
+        <v>6559584</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1968,7 +1968,7 @@
         <v>131128968</v>
       </c>
       <c r="B14" t="n">
-        <v>58258</v>
+        <v>58259</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Enviro Planning, David Alvunger</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2074,7 +2074,7 @@
         <v>131129415</v>
       </c>
       <c r="B15" t="n">
-        <v>58258</v>
+        <v>58259</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>131128965</v>
       </c>
       <c r="B16" t="n">
-        <v>58169</v>
+        <v>58170</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Enviro Planning, David Alvunger</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2286,7 +2286,7 @@
         <v>131129545</v>
       </c>
       <c r="B17" t="n">
-        <v>56769</v>
+        <v>56770</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>131129375</v>
       </c>
       <c r="B18" t="n">
-        <v>58258</v>
+        <v>58259</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>131129574</v>
       </c>
       <c r="B19" t="n">
-        <v>56757</v>
+        <v>56758</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>131129383</v>
       </c>
       <c r="B20" t="n">
-        <v>58567</v>
+        <v>58568</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>131128969</v>
       </c>
       <c r="B21" t="n">
-        <v>58169</v>
+        <v>58170</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Enviro Planning, David Alvunger</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 60553-2025 artfynd.xlsx
+++ b/artfynd/A 60553-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131128956</v>
+        <v>131129356</v>
       </c>
       <c r="B5" t="n">
         <v>58259</v>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532356</v>
+        <v>532317</v>
       </c>
       <c r="R5" t="n">
-        <v>6559685</v>
+        <v>6559623</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,7 +1117,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131129356</v>
+        <v>131128956</v>
       </c>
       <c r="B6" t="n">
         <v>58259</v>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532317</v>
+        <v>532356</v>
       </c>
       <c r="R6" t="n">
-        <v>6559623</v>
+        <v>6559685</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1435,7 +1435,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131128955</v>
+        <v>131128912</v>
       </c>
       <c r="B9" t="n">
         <v>58170</v>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532330</v>
+        <v>532359</v>
       </c>
       <c r="R9" t="n">
-        <v>6559652</v>
+        <v>6559727</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131128912</v>
+        <v>131128955</v>
       </c>
       <c r="B10" t="n">
         <v>58170</v>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532359</v>
+        <v>532330</v>
       </c>
       <c r="R10" t="n">
-        <v>6559727</v>
+        <v>6559652</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1753,7 +1753,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131129360</v>
+        <v>131129013</v>
       </c>
       <c r="B12" t="n">
         <v>58170</v>
@@ -1797,13 +1797,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532346</v>
+        <v>532460</v>
       </c>
       <c r="R12" t="n">
-        <v>6559649</v>
+        <v>6559584</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,7 +1859,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131129013</v>
+        <v>131129360</v>
       </c>
       <c r="B13" t="n">
         <v>58170</v>
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532460</v>
+        <v>532346</v>
       </c>
       <c r="R13" t="n">
-        <v>6559584</v>
+        <v>6559649</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 60553-2025 artfynd.xlsx
+++ b/artfynd/A 60553-2025 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131129377</v>
+        <v>131129587</v>
       </c>
       <c r="B3" t="n">
-        <v>58170</v>
+        <v>56751</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,46 +801,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Segersjö, Nrk</t>
+          <t>Segersjö 1, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532355</v>
+        <v>532339</v>
       </c>
       <c r="R3" t="n">
-        <v>6559582</v>
+        <v>6559657</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,12 +868,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Skogsglänta</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,17 +898,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>David Alvunger, Enviro Planning</t>
+          <t>Alfred Olofsson, Enviro Planning</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131129587</v>
+        <v>131129377</v>
       </c>
       <c r="B4" t="n">
-        <v>56751</v>
+        <v>58170</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,50 +916,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Segersjö 1, Nrk</t>
+          <t>Segersjö, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532339</v>
+        <v>532355</v>
       </c>
       <c r="R4" t="n">
-        <v>6559657</v>
+        <v>6559582</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,17 +979,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Skogsglänta</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,39 +1004,39 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Enviro Planning</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131129356</v>
+        <v>131129319</v>
       </c>
       <c r="B5" t="n">
-        <v>58259</v>
+        <v>58170</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532317</v>
+        <v>532341</v>
       </c>
       <c r="R5" t="n">
-        <v>6559623</v>
+        <v>6559717</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1117,7 +1117,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131128956</v>
+        <v>131129356</v>
       </c>
       <c r="B6" t="n">
         <v>58259</v>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532356</v>
+        <v>532317</v>
       </c>
       <c r="R6" t="n">
-        <v>6559685</v>
+        <v>6559623</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,32 +1223,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131129319</v>
+        <v>131128956</v>
       </c>
       <c r="B7" t="n">
-        <v>58170</v>
+        <v>58259</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532341</v>
+        <v>532356</v>
       </c>
       <c r="R7" t="n">
-        <v>6559717</v>
+        <v>6559685</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1435,7 +1435,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131128912</v>
+        <v>131128955</v>
       </c>
       <c r="B9" t="n">
         <v>58170</v>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532359</v>
+        <v>532330</v>
       </c>
       <c r="R9" t="n">
-        <v>6559727</v>
+        <v>6559652</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131128955</v>
+        <v>131128912</v>
       </c>
       <c r="B10" t="n">
         <v>58170</v>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532330</v>
+        <v>532359</v>
       </c>
       <c r="R10" t="n">
-        <v>6559652</v>
+        <v>6559727</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1753,7 +1753,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131129013</v>
+        <v>131129360</v>
       </c>
       <c r="B12" t="n">
         <v>58170</v>
@@ -1797,13 +1797,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532460</v>
+        <v>532346</v>
       </c>
       <c r="R12" t="n">
-        <v>6559584</v>
+        <v>6559649</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,7 +1859,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131129360</v>
+        <v>131129013</v>
       </c>
       <c r="B13" t="n">
         <v>58170</v>
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532346</v>
+        <v>532460</v>
       </c>
       <c r="R13" t="n">
-        <v>6559649</v>
+        <v>6559584</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1965,7 +1965,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131128968</v>
+        <v>131129415</v>
       </c>
       <c r="B14" t="n">
         <v>58259</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532343</v>
+        <v>532437</v>
       </c>
       <c r="R14" t="n">
-        <v>6559583</v>
+        <v>6559564</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2039,12 +2039,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,7 +2071,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131129415</v>
+        <v>131128968</v>
       </c>
       <c r="B15" t="n">
         <v>58259</v>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532437</v>
+        <v>532343</v>
       </c>
       <c r="R15" t="n">
-        <v>6559564</v>
+        <v>6559583</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2145,12 +2145,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 60553-2025 artfynd.xlsx
+++ b/artfynd/A 60553-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131129561</v>
       </c>
       <c r="B2" t="n">
-        <v>56765</v>
+        <v>56766</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>131129587</v>
       </c>
       <c r="B3" t="n">
-        <v>56751</v>
+        <v>56752</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>131129377</v>
       </c>
       <c r="B4" t="n">
-        <v>58170</v>
+        <v>58171</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,32 +1011,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131129319</v>
+        <v>131128956</v>
       </c>
       <c r="B5" t="n">
-        <v>58170</v>
+        <v>58260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532341</v>
+        <v>532356</v>
       </c>
       <c r="R5" t="n">
-        <v>6559717</v>
+        <v>6559685</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,7 +1120,7 @@
         <v>131129356</v>
       </c>
       <c r="B6" t="n">
-        <v>58259</v>
+        <v>58260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,32 +1223,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131128956</v>
+        <v>131129319</v>
       </c>
       <c r="B7" t="n">
-        <v>58259</v>
+        <v>58171</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532356</v>
+        <v>532341</v>
       </c>
       <c r="R7" t="n">
-        <v>6559685</v>
+        <v>6559717</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,7 +1332,7 @@
         <v>131129381</v>
       </c>
       <c r="B8" t="n">
-        <v>58170</v>
+        <v>58171</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131128955</v>
+        <v>131128912</v>
       </c>
       <c r="B9" t="n">
-        <v>58170</v>
+        <v>58171</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532330</v>
+        <v>532359</v>
       </c>
       <c r="R9" t="n">
-        <v>6559652</v>
+        <v>6559727</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131128912</v>
+        <v>131128955</v>
       </c>
       <c r="B10" t="n">
-        <v>58170</v>
+        <v>58171</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532359</v>
+        <v>532330</v>
       </c>
       <c r="R10" t="n">
-        <v>6559727</v>
+        <v>6559652</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1650,7 +1650,7 @@
         <v>131129373</v>
       </c>
       <c r="B11" t="n">
-        <v>58371</v>
+        <v>58372</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>131129360</v>
       </c>
       <c r="B12" t="n">
-        <v>58170</v>
+        <v>58171</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>131129013</v>
       </c>
       <c r="B13" t="n">
-        <v>58170</v>
+        <v>58171</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1965,10 +1965,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131129415</v>
+        <v>131128968</v>
       </c>
       <c r="B14" t="n">
-        <v>58259</v>
+        <v>58260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532437</v>
+        <v>532343</v>
       </c>
       <c r="R14" t="n">
-        <v>6559564</v>
+        <v>6559583</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2039,12 +2039,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,10 +2071,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131128968</v>
+        <v>131129415</v>
       </c>
       <c r="B15" t="n">
-        <v>58259</v>
+        <v>58260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532343</v>
+        <v>532437</v>
       </c>
       <c r="R15" t="n">
-        <v>6559583</v>
+        <v>6559564</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2145,12 +2145,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2180,7 +2180,7 @@
         <v>131128965</v>
       </c>
       <c r="B16" t="n">
-        <v>58170</v>
+        <v>58171</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>131129545</v>
       </c>
       <c r="B17" t="n">
-        <v>56770</v>
+        <v>56771</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>131129375</v>
       </c>
       <c r="B18" t="n">
-        <v>58259</v>
+        <v>58260</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>131129574</v>
       </c>
       <c r="B19" t="n">
-        <v>56758</v>
+        <v>56759</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>131129383</v>
       </c>
       <c r="B20" t="n">
-        <v>58568</v>
+        <v>58569</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>131128969</v>
       </c>
       <c r="B21" t="n">
-        <v>58170</v>
+        <v>58171</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 60553-2025 artfynd.xlsx
+++ b/artfynd/A 60553-2025 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131129587</v>
+        <v>131129377</v>
       </c>
       <c r="B3" t="n">
-        <v>56752</v>
+        <v>58171</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,50 +801,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Segersjö 1, Nrk</t>
+          <t>Segersjö, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532339</v>
+        <v>532355</v>
       </c>
       <c r="R3" t="n">
-        <v>6559657</v>
+        <v>6559582</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,17 +864,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Skogsglänta</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,17 +889,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Enviro Planning</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131129377</v>
+        <v>131129587</v>
       </c>
       <c r="B4" t="n">
-        <v>58171</v>
+        <v>56752</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,46 +907,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Segersjö, Nrk</t>
+          <t>Segersjö 1, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532355</v>
+        <v>532339</v>
       </c>
       <c r="R4" t="n">
-        <v>6559582</v>
+        <v>6559657</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,12 +974,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Skogsglänta</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>David Alvunger, Enviro Planning</t>
+          <t>Alfred Olofsson, Enviro Planning</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1435,7 +1435,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131128912</v>
+        <v>131128955</v>
       </c>
       <c r="B9" t="n">
         <v>58171</v>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532359</v>
+        <v>532330</v>
       </c>
       <c r="R9" t="n">
-        <v>6559727</v>
+        <v>6559652</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131128955</v>
+        <v>131128912</v>
       </c>
       <c r="B10" t="n">
         <v>58171</v>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532330</v>
+        <v>532359</v>
       </c>
       <c r="R10" t="n">
-        <v>6559652</v>
+        <v>6559727</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>David Alvunger, Enviro Planning</t>
+          <t>Enviro Planning, David Alvunger</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 60553-2025 artfynd.xlsx
+++ b/artfynd/A 60553-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131129561</v>
       </c>
       <c r="B2" t="n">
-        <v>56766</v>
+        <v>56769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>131129377</v>
       </c>
       <c r="B3" t="n">
-        <v>58171</v>
+        <v>58174</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>131129587</v>
       </c>
       <c r="B4" t="n">
-        <v>56752</v>
+        <v>56755</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,32 +1011,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131128956</v>
+        <v>131129319</v>
       </c>
       <c r="B5" t="n">
-        <v>58260</v>
+        <v>58174</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532356</v>
+        <v>532341</v>
       </c>
       <c r="R5" t="n">
-        <v>6559685</v>
+        <v>6559717</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131129356</v>
+        <v>131128956</v>
       </c>
       <c r="B6" t="n">
-        <v>58260</v>
+        <v>58263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532317</v>
+        <v>532356</v>
       </c>
       <c r="R6" t="n">
-        <v>6559623</v>
+        <v>6559685</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,32 +1223,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131129319</v>
+        <v>131129356</v>
       </c>
       <c r="B7" t="n">
-        <v>58171</v>
+        <v>58263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532341</v>
+        <v>532317</v>
       </c>
       <c r="R7" t="n">
-        <v>6559717</v>
+        <v>6559623</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1332,7 +1332,7 @@
         <v>131129381</v>
       </c>
       <c r="B8" t="n">
-        <v>58171</v>
+        <v>58174</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131128955</v>
+        <v>131128912</v>
       </c>
       <c r="B9" t="n">
-        <v>58171</v>
+        <v>58174</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532330</v>
+        <v>532359</v>
       </c>
       <c r="R9" t="n">
-        <v>6559652</v>
+        <v>6559727</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131128912</v>
+        <v>131128955</v>
       </c>
       <c r="B10" t="n">
-        <v>58171</v>
+        <v>58174</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532359</v>
+        <v>532330</v>
       </c>
       <c r="R10" t="n">
-        <v>6559727</v>
+        <v>6559652</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1640,17 +1640,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Enviro Planning, David Alvunger</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131129373</v>
+        <v>131129360</v>
       </c>
       <c r="B11" t="n">
-        <v>58372</v>
+        <v>58174</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,21 +1658,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103018</v>
+        <v>103012</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532335</v>
+        <v>532346</v>
       </c>
       <c r="R11" t="n">
-        <v>6559541</v>
+        <v>6559649</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131129360</v>
+        <v>131129013</v>
       </c>
       <c r="B12" t="n">
-        <v>58171</v>
+        <v>58174</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1797,13 +1797,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532346</v>
+        <v>532460</v>
       </c>
       <c r="R12" t="n">
-        <v>6559649</v>
+        <v>6559584</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,10 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131129013</v>
+        <v>131129373</v>
       </c>
       <c r="B13" t="n">
-        <v>58171</v>
+        <v>58375</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103012</v>
+        <v>103018</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532460</v>
+        <v>532335</v>
       </c>
       <c r="R13" t="n">
-        <v>6559584</v>
+        <v>6559541</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1968,7 +1968,7 @@
         <v>131128968</v>
       </c>
       <c r="B14" t="n">
-        <v>58260</v>
+        <v>58263</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>131129415</v>
       </c>
       <c r="B15" t="n">
-        <v>58260</v>
+        <v>58263</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>131128965</v>
       </c>
       <c r="B16" t="n">
-        <v>58171</v>
+        <v>58174</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>131129545</v>
       </c>
       <c r="B17" t="n">
-        <v>56771</v>
+        <v>56774</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2398,10 +2398,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131129375</v>
+        <v>131129574</v>
       </c>
       <c r="B18" t="n">
-        <v>58260</v>
+        <v>56762</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2409,21 +2409,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>205992</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2431,24 +2431,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Segersjö, Nrk</t>
+          <t>Segersjö 1, Nrk</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532358</v>
+        <v>532339</v>
       </c>
       <c r="R18" t="n">
-        <v>6559555</v>
+        <v>6559657</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2472,12 +2476,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Skogsglänta</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,17 +2506,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>David Alvunger, Enviro Planning</t>
+          <t>Alfred Olofsson, Enviro Planning</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131129574</v>
+        <v>131129375</v>
       </c>
       <c r="B19" t="n">
-        <v>56759</v>
+        <v>58263</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,21 +2524,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205992</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2537,28 +2546,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Segersjö 1, Nrk</t>
+          <t>Segersjö, Nrk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532339</v>
+        <v>532358</v>
       </c>
       <c r="R19" t="n">
-        <v>6559657</v>
+        <v>6559555</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2582,17 +2587,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Skogsglänta</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Enviro Planning</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2622,7 +2622,7 @@
         <v>131129383</v>
       </c>
       <c r="B20" t="n">
-        <v>58569</v>
+        <v>58572</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>131128969</v>
       </c>
       <c r="B21" t="n">
-        <v>58171</v>
+        <v>58174</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 60553-2025 artfynd.xlsx
+++ b/artfynd/A 60553-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131129561</v>
       </c>
       <c r="B2" t="n">
-        <v>56769</v>
+        <v>56770</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131129377</v>
+        <v>131129587</v>
       </c>
       <c r="B3" t="n">
-        <v>58174</v>
+        <v>56756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,46 +801,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Segersjö, Nrk</t>
+          <t>Segersjö 1, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532355</v>
+        <v>532339</v>
       </c>
       <c r="R3" t="n">
-        <v>6559582</v>
+        <v>6559657</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,12 +868,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Skogsglänta</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,17 +898,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>David Alvunger, Enviro Planning</t>
+          <t>Alfred Olofsson, Enviro Planning</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131129587</v>
+        <v>131129377</v>
       </c>
       <c r="B4" t="n">
-        <v>56755</v>
+        <v>58175</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,50 +916,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Segersjö 1, Nrk</t>
+          <t>Segersjö, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532339</v>
+        <v>532355</v>
       </c>
       <c r="R4" t="n">
-        <v>6559657</v>
+        <v>6559582</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,17 +979,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Skogsglänta</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,39 +1004,39 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Enviro Planning</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131129319</v>
+        <v>131129356</v>
       </c>
       <c r="B5" t="n">
-        <v>58174</v>
+        <v>58264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532341</v>
+        <v>532317</v>
       </c>
       <c r="R5" t="n">
-        <v>6559717</v>
+        <v>6559623</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1117,32 +1117,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131128956</v>
+        <v>131129319</v>
       </c>
       <c r="B6" t="n">
-        <v>58263</v>
+        <v>58175</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532356</v>
+        <v>532341</v>
       </c>
       <c r="R6" t="n">
-        <v>6559685</v>
+        <v>6559717</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,10 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131129356</v>
+        <v>131128956</v>
       </c>
       <c r="B7" t="n">
-        <v>58263</v>
+        <v>58264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532317</v>
+        <v>532356</v>
       </c>
       <c r="R7" t="n">
-        <v>6559623</v>
+        <v>6559685</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,7 +1332,7 @@
         <v>131129381</v>
       </c>
       <c r="B8" t="n">
-        <v>58174</v>
+        <v>58175</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131128912</v>
+        <v>131128955</v>
       </c>
       <c r="B9" t="n">
-        <v>58174</v>
+        <v>58175</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532359</v>
+        <v>532330</v>
       </c>
       <c r="R9" t="n">
-        <v>6559727</v>
+        <v>6559652</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131128955</v>
+        <v>131128912</v>
       </c>
       <c r="B10" t="n">
-        <v>58174</v>
+        <v>58175</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532330</v>
+        <v>532359</v>
       </c>
       <c r="R10" t="n">
-        <v>6559652</v>
+        <v>6559727</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1647,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131129360</v>
+        <v>131129373</v>
       </c>
       <c r="B11" t="n">
-        <v>58174</v>
+        <v>58376</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,21 +1658,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103012</v>
+        <v>103018</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532346</v>
+        <v>532335</v>
       </c>
       <c r="R11" t="n">
-        <v>6559649</v>
+        <v>6559541</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131129013</v>
+        <v>131129360</v>
       </c>
       <c r="B12" t="n">
-        <v>58174</v>
+        <v>58175</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1797,13 +1797,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532460</v>
+        <v>532346</v>
       </c>
       <c r="R12" t="n">
-        <v>6559584</v>
+        <v>6559649</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,10 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131129373</v>
+        <v>131129013</v>
       </c>
       <c r="B13" t="n">
-        <v>58375</v>
+        <v>58175</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103018</v>
+        <v>103012</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532335</v>
+        <v>532460</v>
       </c>
       <c r="R13" t="n">
-        <v>6559541</v>
+        <v>6559584</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1968,7 +1968,7 @@
         <v>131128968</v>
       </c>
       <c r="B14" t="n">
-        <v>58263</v>
+        <v>58264</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>131129415</v>
       </c>
       <c r="B15" t="n">
-        <v>58263</v>
+        <v>58264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>131128965</v>
       </c>
       <c r="B16" t="n">
-        <v>58174</v>
+        <v>58175</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>131129545</v>
       </c>
       <c r="B17" t="n">
-        <v>56774</v>
+        <v>56775</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2398,10 +2398,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131129574</v>
+        <v>131129375</v>
       </c>
       <c r="B18" t="n">
-        <v>56762</v>
+        <v>58264</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2409,21 +2409,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>205992</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2431,28 +2431,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Segersjö 1, Nrk</t>
+          <t>Segersjö, Nrk</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532339</v>
+        <v>532358</v>
       </c>
       <c r="R18" t="n">
-        <v>6559657</v>
+        <v>6559555</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2476,17 +2472,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Skogsglänta</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2506,17 +2497,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Enviro Planning</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131129375</v>
+        <v>131129574</v>
       </c>
       <c r="B19" t="n">
-        <v>58263</v>
+        <v>56763</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,21 +2515,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>205992</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2546,24 +2537,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Segersjö, Nrk</t>
+          <t>Segersjö 1, Nrk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532358</v>
+        <v>532339</v>
       </c>
       <c r="R19" t="n">
-        <v>6559555</v>
+        <v>6559657</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2587,12 +2582,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Skogsglänta</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>David Alvunger, Enviro Planning</t>
+          <t>Alfred Olofsson, Enviro Planning</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2622,7 +2622,7 @@
         <v>131129383</v>
       </c>
       <c r="B20" t="n">
-        <v>58572</v>
+        <v>58573</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>131128969</v>
       </c>
       <c r="B21" t="n">
-        <v>58174</v>
+        <v>58175</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 60553-2025 artfynd.xlsx
+++ b/artfynd/A 60553-2025 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131129587</v>
+        <v>131129377</v>
       </c>
       <c r="B3" t="n">
-        <v>56756</v>
+        <v>58175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,50 +801,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Segersjö 1, Nrk</t>
+          <t>Segersjö, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532339</v>
+        <v>532355</v>
       </c>
       <c r="R3" t="n">
-        <v>6559657</v>
+        <v>6559582</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,17 +864,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Skogsglänta</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,17 +889,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Enviro Planning</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131129377</v>
+        <v>131129587</v>
       </c>
       <c r="B4" t="n">
-        <v>58175</v>
+        <v>56756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,46 +907,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Segersjö, Nrk</t>
+          <t>Segersjö 1, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532355</v>
+        <v>532339</v>
       </c>
       <c r="R4" t="n">
-        <v>6559582</v>
+        <v>6559657</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,12 +974,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Skogsglänta</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,39 +1004,39 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>David Alvunger, Enviro Planning</t>
+          <t>Alfred Olofsson, Enviro Planning</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131129356</v>
+        <v>131129319</v>
       </c>
       <c r="B5" t="n">
-        <v>58264</v>
+        <v>58175</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532317</v>
+        <v>532341</v>
       </c>
       <c r="R5" t="n">
-        <v>6559623</v>
+        <v>6559717</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1117,32 +1117,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131129319</v>
+        <v>131129356</v>
       </c>
       <c r="B6" t="n">
-        <v>58175</v>
+        <v>58264</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532341</v>
+        <v>532317</v>
       </c>
       <c r="R6" t="n">
-        <v>6559717</v>
+        <v>6559623</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 60553-2025 artfynd.xlsx
+++ b/artfynd/A 60553-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131129561</v>
       </c>
       <c r="B2" t="n">
-        <v>56770</v>
+        <v>56775</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131129377</v>
+        <v>131129587</v>
       </c>
       <c r="B3" t="n">
-        <v>58175</v>
+        <v>56761</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,46 +801,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Segersjö, Nrk</t>
+          <t>Segersjö 1, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532355</v>
+        <v>532339</v>
       </c>
       <c r="R3" t="n">
-        <v>6559582</v>
+        <v>6559657</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,12 +868,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Skogsglänta</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,17 +898,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>David Alvunger, Enviro Planning</t>
+          <t>Alfred Olofsson, Enviro Planning</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131129587</v>
+        <v>131129377</v>
       </c>
       <c r="B4" t="n">
-        <v>56756</v>
+        <v>58180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,50 +916,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Segersjö 1, Nrk</t>
+          <t>Segersjö, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532339</v>
+        <v>532355</v>
       </c>
       <c r="R4" t="n">
-        <v>6559657</v>
+        <v>6559582</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,17 +979,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Skogsglänta</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Enviro Planning</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1014,7 +1014,7 @@
         <v>131129319</v>
       </c>
       <c r="B5" t="n">
-        <v>58175</v>
+        <v>58180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131129356</v>
+        <v>131128956</v>
       </c>
       <c r="B6" t="n">
-        <v>58264</v>
+        <v>58269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532317</v>
+        <v>532356</v>
       </c>
       <c r="R6" t="n">
-        <v>6559623</v>
+        <v>6559685</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,10 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131128956</v>
+        <v>131129356</v>
       </c>
       <c r="B7" t="n">
-        <v>58264</v>
+        <v>58269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532356</v>
+        <v>532317</v>
       </c>
       <c r="R7" t="n">
-        <v>6559685</v>
+        <v>6559623</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,7 +1332,7 @@
         <v>131129381</v>
       </c>
       <c r="B8" t="n">
-        <v>58175</v>
+        <v>58180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>131128955</v>
       </c>
       <c r="B9" t="n">
-        <v>58175</v>
+        <v>58180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>131128912</v>
       </c>
       <c r="B10" t="n">
-        <v>58175</v>
+        <v>58180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131129373</v>
+        <v>131129360</v>
       </c>
       <c r="B11" t="n">
-        <v>58376</v>
+        <v>58180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,21 +1658,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103018</v>
+        <v>103012</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532335</v>
+        <v>532346</v>
       </c>
       <c r="R11" t="n">
-        <v>6559541</v>
+        <v>6559649</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131129360</v>
+        <v>131129013</v>
       </c>
       <c r="B12" t="n">
-        <v>58175</v>
+        <v>58180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1797,13 +1797,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532346</v>
+        <v>532460</v>
       </c>
       <c r="R12" t="n">
-        <v>6559649</v>
+        <v>6559584</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,10 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131129013</v>
+        <v>131129373</v>
       </c>
       <c r="B13" t="n">
-        <v>58175</v>
+        <v>58381</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103012</v>
+        <v>103018</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532460</v>
+        <v>532335</v>
       </c>
       <c r="R13" t="n">
-        <v>6559584</v>
+        <v>6559541</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1968,7 +1968,7 @@
         <v>131128968</v>
       </c>
       <c r="B14" t="n">
-        <v>58264</v>
+        <v>58269</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>131129415</v>
       </c>
       <c r="B15" t="n">
-        <v>58264</v>
+        <v>58269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>131128965</v>
       </c>
       <c r="B16" t="n">
-        <v>58175</v>
+        <v>58180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>131129545</v>
       </c>
       <c r="B17" t="n">
-        <v>56775</v>
+        <v>56780</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2398,10 +2398,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131129375</v>
+        <v>131129574</v>
       </c>
       <c r="B18" t="n">
-        <v>58264</v>
+        <v>56768</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2409,21 +2409,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>205992</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2431,24 +2431,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Segersjö, Nrk</t>
+          <t>Segersjö 1, Nrk</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532358</v>
+        <v>532339</v>
       </c>
       <c r="R18" t="n">
-        <v>6559555</v>
+        <v>6559657</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2472,12 +2476,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Skogsglänta</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,17 +2506,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>David Alvunger, Enviro Planning</t>
+          <t>Alfred Olofsson, Enviro Planning</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131129574</v>
+        <v>131129375</v>
       </c>
       <c r="B19" t="n">
-        <v>56763</v>
+        <v>58269</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,21 +2524,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205992</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2537,28 +2546,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Segersjö 1, Nrk</t>
+          <t>Segersjö, Nrk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532339</v>
+        <v>532358</v>
       </c>
       <c r="R19" t="n">
-        <v>6559657</v>
+        <v>6559555</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2582,17 +2587,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Skogsglänta</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Enviro Planning</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2622,7 +2622,7 @@
         <v>131129383</v>
       </c>
       <c r="B20" t="n">
-        <v>58573</v>
+        <v>58578</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>131128969</v>
       </c>
       <c r="B21" t="n">
-        <v>58175</v>
+        <v>58180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 60553-2025 artfynd.xlsx
+++ b/artfynd/A 60553-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131129561</v>
+        <v>131129560</v>
       </c>
       <c r="B2" t="n">
-        <v>56775</v>
+        <v>56830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -753,12 +753,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131129587</v>
+        <v>131128912</v>
       </c>
       <c r="B3" t="n">
-        <v>56761</v>
+        <v>58238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -823,28 +823,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Segersjö 1, Nrk</t>
+          <t>Segersjö, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532339</v>
+        <v>532359</v>
       </c>
       <c r="R3" t="n">
-        <v>6559657</v>
+        <v>6559727</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,17 +864,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Skogsglänta</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,17 +889,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Enviro Planning</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131129377</v>
+        <v>131128955</v>
       </c>
       <c r="B4" t="n">
-        <v>58180</v>
+        <v>58238</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,7 +926,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -949,13 +940,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532355</v>
+        <v>532330</v>
       </c>
       <c r="R4" t="n">
-        <v>6559582</v>
+        <v>6559652</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,12 +970,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131129319</v>
+        <v>131128965</v>
       </c>
       <c r="B5" t="n">
-        <v>58180</v>
+        <v>58238</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1055,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532341</v>
+        <v>532445</v>
       </c>
       <c r="R5" t="n">
-        <v>6559717</v>
+        <v>6559651</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1085,12 +1076,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,32 +1108,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131128956</v>
+        <v>131128969</v>
       </c>
       <c r="B6" t="n">
-        <v>58269</v>
+        <v>58238</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1164,7 +1155,7 @@
         <v>532356</v>
       </c>
       <c r="R6" t="n">
-        <v>6559685</v>
+        <v>6559613</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1223,32 +1214,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131129356</v>
+        <v>131129013</v>
       </c>
       <c r="B7" t="n">
-        <v>58269</v>
+        <v>58238</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1267,13 +1258,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532317</v>
+        <v>532460</v>
       </c>
       <c r="R7" t="n">
-        <v>6559623</v>
+        <v>6559584</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1297,12 +1288,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131129381</v>
+        <v>131129319</v>
       </c>
       <c r="B8" t="n">
-        <v>58180</v>
+        <v>58238</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532301</v>
+        <v>532341</v>
       </c>
       <c r="R8" t="n">
-        <v>6559577</v>
+        <v>6559717</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1435,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131128955</v>
+        <v>131129360</v>
       </c>
       <c r="B9" t="n">
-        <v>58180</v>
+        <v>58238</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532330</v>
+        <v>532346</v>
       </c>
       <c r="R9" t="n">
-        <v>6559652</v>
+        <v>6559649</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1509,12 +1500,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,10 +1532,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131128912</v>
+        <v>131129377</v>
       </c>
       <c r="B10" t="n">
-        <v>58180</v>
+        <v>58238</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1562,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1585,13 +1576,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532359</v>
+        <v>532355</v>
       </c>
       <c r="R10" t="n">
-        <v>6559727</v>
+        <v>6559582</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1615,12 +1606,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1647,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131129360</v>
+        <v>131129381</v>
       </c>
       <c r="B11" t="n">
-        <v>58180</v>
+        <v>58238</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1691,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532346</v>
+        <v>532301</v>
       </c>
       <c r="R11" t="n">
-        <v>6559649</v>
+        <v>6559577</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1753,32 +1744,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131129013</v>
+        <v>131128956</v>
       </c>
       <c r="B12" t="n">
-        <v>58180</v>
+        <v>58327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1797,13 +1788,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532460</v>
+        <v>532356</v>
       </c>
       <c r="R12" t="n">
-        <v>6559584</v>
+        <v>6559685</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1859,32 +1850,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131129373</v>
+        <v>131128966</v>
       </c>
       <c r="B13" t="n">
-        <v>58381</v>
+        <v>58327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1903,10 +1894,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532335</v>
+        <v>532480</v>
       </c>
       <c r="R13" t="n">
-        <v>6559541</v>
+        <v>6559631</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1933,12 +1924,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1968,7 +1959,7 @@
         <v>131128968</v>
       </c>
       <c r="B14" t="n">
-        <v>58269</v>
+        <v>58327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2071,10 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131129415</v>
+        <v>131129356</v>
       </c>
       <c r="B15" t="n">
-        <v>58269</v>
+        <v>58327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532437</v>
+        <v>532317</v>
       </c>
       <c r="R15" t="n">
-        <v>6559564</v>
+        <v>6559623</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2177,32 +2168,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131128965</v>
+        <v>131129375</v>
       </c>
       <c r="B16" t="n">
-        <v>58180</v>
+        <v>58327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2221,10 +2212,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>532445</v>
+        <v>532358</v>
       </c>
       <c r="R16" t="n">
-        <v>6559651</v>
+        <v>6559555</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2251,12 +2242,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2283,10 +2274,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131129545</v>
+        <v>131129415</v>
       </c>
       <c r="B17" t="n">
-        <v>56780</v>
+        <v>58327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,50 +2285,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205995</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Segersjö 1, Nrk</t>
+          <t>Segersjö, Nrk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>532339</v>
+        <v>532437</v>
       </c>
       <c r="R17" t="n">
-        <v>6559657</v>
+        <v>6559564</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2361,17 +2348,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Skogsglänta</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2391,17 +2373,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Enviro Planning</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131129574</v>
+        <v>131128910</v>
       </c>
       <c r="B18" t="n">
-        <v>56768</v>
+        <v>58439</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2409,21 +2391,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>205992</v>
+        <v>103018</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2431,28 +2413,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Segersjö 1, Nrk</t>
+          <t>Segersjö, Nrk</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532339</v>
+        <v>532421</v>
       </c>
       <c r="R18" t="n">
-        <v>6559657</v>
+        <v>6559750</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2476,17 +2454,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Skogsglänta</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2506,17 +2479,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Enviro Planning</t>
+          <t>David Alvunger, Enviro Planning</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131129375</v>
+        <v>131128915</v>
       </c>
       <c r="B19" t="n">
-        <v>58269</v>
+        <v>58439</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,21 +2497,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>103018</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2557,10 +2530,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532358</v>
+        <v>532319</v>
       </c>
       <c r="R19" t="n">
-        <v>6559555</v>
+        <v>6559729</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2587,12 +2560,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2619,10 +2592,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131129383</v>
+        <v>131129364</v>
       </c>
       <c r="B20" t="n">
-        <v>58578</v>
+        <v>58439</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,31 +2603,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2663,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>532283</v>
+        <v>532458</v>
       </c>
       <c r="R20" t="n">
-        <v>6559559</v>
+        <v>6559685</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2725,32 +2698,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131128969</v>
+        <v>131129373</v>
       </c>
       <c r="B21" t="n">
-        <v>58180</v>
+        <v>58439</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103012</v>
+        <v>103018</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2769,10 +2742,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>532356</v>
+        <v>532335</v>
       </c>
       <c r="R21" t="n">
-        <v>6559613</v>
+        <v>6559541</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2799,12 +2772,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2828,6 +2801,457 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131129383</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Segersjö, Nrk</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>532283</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6559559</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lännäs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>David Alvunger</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>David Alvunger, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131129574</v>
+      </c>
+      <c r="B23" t="n">
+        <v>56823</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Segersjö 1, Nrk</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>532339</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6559657</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lännäs</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Skogsglänta</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>David Alvunger</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131129545</v>
+      </c>
+      <c r="B24" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Segersjö 1, Nrk</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>532339</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6559657</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lännäs</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Skogsglänta</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>David Alvunger</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131129587</v>
+      </c>
+      <c r="B25" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Segersjö 1, Nrk</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>532339</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6559657</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lännäs</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Skogsglänta</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>David Alvunger</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
